--- a/Data/EXCEL/Transfer/dividend/20260225_0_4/1806-dividend-20260225_0_4.xlsx
+++ b/Data/EXCEL/Transfer/dividend/20260225_0_4/1806-dividend-20260225_0_4.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspaces\xls2xlxs\20260225_0_4\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Workspaces\xls2xlsx\transfer\20260225_0_4\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{3F084C29-0036-41D1-94EE-E3D3ADC785FC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{D093A0C3-2860-49C9-A376-28CBB0103C1D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4140" yWindow="576" windowWidth="16656" windowHeight="10992" xr2:uid="{BCA6910E-C0CC-4E54-8008-18E8ED5F7489}"/>
+    <workbookView xWindow="780" yWindow="780" windowWidth="22845" windowHeight="19530" xr2:uid="{C8FADBF8-8BDB-46DC-9346-6A486740893E}"/>
   </bookViews>
   <sheets>
     <sheet name="1806-dividend-20260225_0_4" sheetId="1" r:id="rId1"/>
@@ -1427,25 +1427,25 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4176ADC7-A61A-4C1E-9DEF-DE0B0B044BC7}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B5691F50-5C16-462F-9A12-8C3112123760}">
   <dimension ref="A1:R44"/>
-  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="5.109375" customWidth="1"/>
-    <col min="2" max="2" width="5.88671875" customWidth="1"/>
-    <col min="3" max="3" width="8" customWidth="1"/>
-    <col min="4" max="4" width="8.33203125" customWidth="1"/>
-    <col min="5" max="5" width="8" customWidth="1"/>
-    <col min="6" max="7" width="8.33203125" customWidth="1"/>
-    <col min="8" max="8" width="8" customWidth="1"/>
-    <col min="9" max="10" width="8.33203125" customWidth="1"/>
-    <col min="11" max="13" width="8" customWidth="1"/>
-    <col min="14" max="14" width="8.33203125" customWidth="1"/>
-    <col min="15" max="17" width="8" customWidth="1"/>
-    <col min="18" max="18" width="9.33203125" customWidth="1"/>
+    <col min="1" max="1" width="6.5" customWidth="1"/>
+    <col min="2" max="2" width="7.5" customWidth="1"/>
+    <col min="3" max="3" width="10" customWidth="1"/>
+    <col min="4" max="4" width="10.5" customWidth="1"/>
+    <col min="5" max="5" width="10" customWidth="1"/>
+    <col min="6" max="7" width="10.5" customWidth="1"/>
+    <col min="8" max="8" width="10" customWidth="1"/>
+    <col min="9" max="10" width="10.5" customWidth="1"/>
+    <col min="11" max="13" width="10" customWidth="1"/>
+    <col min="14" max="14" width="10.5" customWidth="1"/>
+    <col min="15" max="17" width="10" customWidth="1"/>
+    <col min="18" max="18" width="11.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" s="1" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:18" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A1" s="19" t="s">
         <v>0</v>
       </c>
@@ -1473,7 +1473,7 @@
       <c r="Q1" s="28"/>
       <c r="R1" s="20"/>
     </row>
-    <row r="2" spans="1:18" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:18" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A2" s="21" t="s">
         <v>1</v>
       </c>
@@ -1503,7 +1503,7 @@
       <c r="Q2" s="30"/>
       <c r="R2" s="31"/>
     </row>
-    <row r="3" spans="1:18" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:18" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A3" s="21" t="s">
         <v>2</v>
       </c>
@@ -1549,7 +1549,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="4" spans="1:18" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:18" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A4" s="23"/>
       <c r="B4" s="24"/>
       <c r="C4" s="7"/>
@@ -1599,7 +1599,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="5" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A5" s="35">
         <v>2025</v>
       </c>
@@ -1653,7 +1653,7 @@
         <v>8.4</v>
       </c>
     </row>
-    <row r="6" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A6" s="11" t="s">
         <v>25</v>
       </c>
@@ -1709,7 +1709,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A7" s="11" t="s">
         <v>25</v>
       </c>
@@ -1765,7 +1765,7 @@
         <v>8.4</v>
       </c>
     </row>
-    <row r="8" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A8" s="37">
         <v>2024</v>
       </c>
@@ -1819,7 +1819,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A9" s="35">
         <v>2023</v>
       </c>
@@ -1873,7 +1873,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A10" s="37">
         <v>2022</v>
       </c>
@@ -1927,7 +1927,7 @@
         <v>9.1300000000000008</v>
       </c>
     </row>
-    <row r="11" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A11" s="35">
         <v>2021</v>
       </c>
@@ -1981,7 +1981,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A12" s="37">
         <v>2020</v>
       </c>
@@ -2035,7 +2035,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A13" s="35">
         <v>2019</v>
       </c>
@@ -2089,7 +2089,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A14" s="37">
         <v>2018</v>
       </c>
@@ -2143,7 +2143,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A15" s="35">
         <v>2017</v>
       </c>
@@ -2197,7 +2197,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A16" s="37">
         <v>2016</v>
       </c>
@@ -2251,7 +2251,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A17" s="35">
         <v>2015</v>
       </c>
@@ -2305,7 +2305,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A18" s="37">
         <v>2014</v>
       </c>
@@ -2359,7 +2359,7 @@
         <v>0.98</v>
       </c>
     </row>
-    <row r="19" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A19" s="35">
         <v>2013</v>
       </c>
@@ -2413,7 +2413,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A20" s="37">
         <v>2012</v>
       </c>
@@ -2467,7 +2467,7 @@
         <v>4.59</v>
       </c>
     </row>
-    <row r="21" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A21" s="35">
         <v>2011</v>
       </c>
@@ -2521,7 +2521,7 @@
         <v>6.13</v>
       </c>
     </row>
-    <row r="22" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A22" s="37">
         <v>2010</v>
       </c>
@@ -2575,7 +2575,7 @@
         <v>3.53</v>
       </c>
     </row>
-    <row r="23" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A23" s="35">
         <v>2009</v>
       </c>
@@ -2629,7 +2629,7 @@
         <v>1.32</v>
       </c>
     </row>
-    <row r="24" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A24" s="37">
         <v>2008</v>
       </c>
@@ -2683,7 +2683,7 @@
         <v>10.4</v>
       </c>
     </row>
-    <row r="25" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A25" s="35">
         <v>2007</v>
       </c>
@@ -2737,7 +2737,7 @@
         <v>3.52</v>
       </c>
     </row>
-    <row r="26" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A26" s="37">
         <v>2006</v>
       </c>
@@ -2791,7 +2791,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A27" s="35">
         <v>2005</v>
       </c>
@@ -2845,7 +2845,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A28" s="37">
         <v>2004</v>
       </c>
@@ -2899,7 +2899,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A29" s="35">
         <v>2003</v>
       </c>
@@ -2953,7 +2953,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A30" s="37">
         <v>2002</v>
       </c>
@@ -3007,7 +3007,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A31" s="35">
         <v>2001</v>
       </c>
@@ -3061,7 +3061,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A32" s="37">
         <v>2000</v>
       </c>
@@ -3115,7 +3115,7 @@
         <v>4.71</v>
       </c>
     </row>
-    <row r="33" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A33" s="35">
         <v>1999</v>
       </c>
@@ -3169,7 +3169,7 @@
         <v>1.26</v>
       </c>
     </row>
-    <row r="34" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A34" s="37">
         <v>1998</v>
       </c>
@@ -3223,7 +3223,7 @@
         <v>6.73</v>
       </c>
     </row>
-    <row r="35" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A35" s="35">
         <v>1997</v>
       </c>
@@ -3277,7 +3277,7 @@
         <v>1.22</v>
       </c>
     </row>
-    <row r="36" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A36" s="37">
         <v>1996</v>
       </c>
@@ -3331,7 +3331,7 @@
         <v>7.49</v>
       </c>
     </row>
-    <row r="37" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A37" s="35">
         <v>1995</v>
       </c>
@@ -3385,7 +3385,7 @@
         <v>7.92</v>
       </c>
     </row>
-    <row r="38" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A38" s="37">
         <v>1994</v>
       </c>
@@ -3439,7 +3439,7 @@
         <v>4.78</v>
       </c>
     </row>
-    <row r="39" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A39" s="35">
         <v>1993</v>
       </c>
@@ -3493,7 +3493,7 @@
         <v>4.38</v>
       </c>
     </row>
-    <row r="40" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A40" s="37">
         <v>1992</v>
       </c>
@@ -3547,7 +3547,7 @@
         <v>3.96</v>
       </c>
     </row>
-    <row r="41" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A41" s="35">
         <v>1991</v>
       </c>
@@ -3601,7 +3601,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="42" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A42" s="37">
         <v>1990</v>
       </c>
@@ -3655,7 +3655,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="43" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A43" s="35">
         <v>1989</v>
       </c>
@@ -3709,7 +3709,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="44" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A44" s="37" t="s">
         <v>30</v>
       </c>
